--- a/感想.xlsx
+++ b/感想.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA2B\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takum\Desktop\Teams\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A8FEA1-C635-439E-A5DF-A5809E4F80D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9420"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -374,7 +375,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -429,11 +430,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -441,7 +441,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -718,11 +718,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="55.125" customWidth="1"/>
+    <col min="1" max="1" width="85.5" customWidth="1"/>
     <col min="2" max="2" width="82.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -734,7 +734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -742,17 +742,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -760,7 +760,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -768,12 +768,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -781,45 +781,45 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" s="2" t="s">
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="1:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -827,7 +827,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -835,7 +835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>26</v>
       </c>

--- a/感想.xlsx
+++ b/感想.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takum\Desktop\Teams\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA2B\Desktop\2BTeam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A8FEA1-C635-439E-A5DF-A5809E4F80D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>感想</t>
     <rPh sb="0" eb="2">
@@ -370,12 +369,140 @@
   </si>
   <si>
     <t>全体的に完成度の高いゲームだとかんじました。たのしかったです。</t>
+  </si>
+  <si>
+    <t>以下、２Bの感想</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>面白かったです</t>
+    <rPh sb="0" eb="2">
+      <t>オモシロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空飛んでるときに敵をロックオンしながら後ろに下がると上に上がっていく＆飛んでいる時に前後左右に動かすとスタミナを消費せずその高さにいれる</t>
+    <rPh sb="0" eb="1">
+      <t>ソラ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ウシ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ゼンゴ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>サユウ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>凄くよくできていました</t>
+    <rPh sb="0" eb="1">
+      <t>スゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>とてもレベルが高く面白かった</t>
+    <rPh sb="7" eb="8">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>オモシロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やりごたえがあった</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>単純に操作が楽しかった。</t>
+    <rPh sb="0" eb="2">
+      <t>タンジュン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が銃を持っていない/ボスの出現と攻撃が早くて初見では会費が難しい</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジュウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ハヤ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ショケン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カイヒ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ムズカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -441,7 +568,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="標準 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -718,8 +845,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="85.5" customWidth="1"/>
@@ -840,6 +967,42 @@
         <v>26</v>
       </c>
     </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
